--- a/templates/delivery_note_gauge_xingnan.xlsx
+++ b/templates/delivery_note_gauge_xingnan.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>送货日期</t>
   </si>
@@ -59,7 +59,7 @@
     <t>{{order_no}}</t>
   </si>
   <si>
-    <t/>
+    <t>{{customer_path}}</t>
   </si>
   <si>
     <t>{{drawing_no}}</t>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>{{quantity}}</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>{{system_delivery_date}}</t>
@@ -17106,13 +17109,13 @@
         <v>17</v>
       </c>
       <c r="G5" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s" s="12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -17122,28 +17125,28 @@
         <v>12</v>
       </c>
       <c r="B6" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H6" t="s" s="13">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -17153,28 +17156,28 @@
         <v>12</v>
       </c>
       <c r="B7" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -17184,28 +17187,28 @@
         <v>12</v>
       </c>
       <c r="B8" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H8" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -17215,28 +17218,28 @@
         <v>12</v>
       </c>
       <c r="B9" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H9" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -17246,28 +17249,28 @@
         <v>12</v>
       </c>
       <c r="B10" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -17277,28 +17280,28 @@
         <v>12</v>
       </c>
       <c r="B11" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H11" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -17308,28 +17311,28 @@
         <v>12</v>
       </c>
       <c r="B12" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G12" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s" s="13">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -17339,28 +17342,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s" s="16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s" s="17">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s" s="6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -17370,28 +17373,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s" s="16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s" s="17">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s" s="18">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -17401,28 +17404,28 @@
         <v>12</v>
       </c>
       <c r="B15" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s" s="16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G15" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H15" t="s" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -17432,28 +17435,28 @@
         <v>12</v>
       </c>
       <c r="B16" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s" s="16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G16" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H16" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -17463,28 +17466,28 @@
         <v>12</v>
       </c>
       <c r="B17" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s" s="16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G17" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H17" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -17494,28 +17497,28 @@
         <v>12</v>
       </c>
       <c r="B18" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s" s="16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G18" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H18" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -17525,28 +17528,28 @@
         <v>12</v>
       </c>
       <c r="B19" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s" s="16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F19" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G19" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H19" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I19" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -17556,28 +17559,28 @@
         <v>12</v>
       </c>
       <c r="B20" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s" s="16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F20" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G20" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H20" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -17587,28 +17590,28 @@
         <v>12</v>
       </c>
       <c r="B21" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E21" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s" s="16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G21" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H21" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I21" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -17618,28 +17621,28 @@
         <v>12</v>
       </c>
       <c r="B22" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D22" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s" s="16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G22" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H22" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I22" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -17649,28 +17652,28 @@
         <v>12</v>
       </c>
       <c r="B23" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D23" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E23" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F23" t="s" s="16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G23" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H23" t="s" s="19">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -17680,28 +17683,28 @@
         <v>12</v>
       </c>
       <c r="B24" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F24" t="s" s="16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G24" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H24" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -17711,28 +17714,28 @@
         <v>12</v>
       </c>
       <c r="B25" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D25" t="s" s="16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F25" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G25" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H25" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I25" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -17742,28 +17745,28 @@
         <v>12</v>
       </c>
       <c r="B26" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D26" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E26" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F26" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G26" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H26" t="s" s="19">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -17773,28 +17776,28 @@
         <v>12</v>
       </c>
       <c r="B27" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D27" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E27" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F27" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G27" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H27" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -17804,28 +17807,28 @@
         <v>12</v>
       </c>
       <c r="B28" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D28" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E28" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F28" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G28" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H28" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -17835,35 +17838,35 @@
         <v>12</v>
       </c>
       <c r="B29" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D29" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F29" t="s" s="10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G29" t="s" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H29" t="s" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" t="s" s="20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
@@ -17879,7 +17882,7 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20"/>
       <c r="B31" t="s" s="20">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="20"/>
